--- a/Result/profitability/3138.xlsx
+++ b/Result/profitability/3138.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM52"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35125</v>
+        <v>0.2725</v>
       </c>
       <c r="N2" t="n">
-        <v>38.73</v>
+        <v>39.17625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13375</v>
+        <v>0.08249999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>36.2575</v>
+        <v>36.7775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.006249999999999999</v>
+        <v>0.07125000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>33.68375</v>
+        <v>34.65125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04625</v>
+        <v>0.08249999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>31.07375</v>
+        <v>31.56375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06625</v>
+        <v>-0.03749999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>29.23125</v>
+        <v>29.655</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1025</v>
+        <v>-0.1925</v>
       </c>
       <c r="N7" t="n">
-        <v>27.5875</v>
+        <v>28.065</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -7032,6 +7032,133 @@
       </c>
       <c r="AM52" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>450</v>
+      </c>
+      <c r="D53" t="n">
+        <v>247</v>
+      </c>
+      <c r="E53" t="n">
+        <v>203</v>
+      </c>
+      <c r="F53" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="G53" t="n">
+        <v>20</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4.33%</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>19</v>
+      </c>
+      <c r="K53" t="n">
+        <v>22</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.4737499999999999</v>
+      </c>
+      <c r="N53" t="n">
+        <v>41.335</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="X53" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.08880308880308885</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-1.661290322580645</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.919999999999995</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.09514563106796103</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
